--- a/Automation/Test Case Automate IPG.xlsx
+++ b/Automation/Test Case Automate IPG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ardhiansyah.nugroho\git\Automate-Katalon-Dashboard-IPG\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55216B9F-194E-4522-B725-B64B3E004C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D281CB32-0221-4779-A422-59E40B1BF2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sale" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
   <si>
     <t>Data Kartu</t>
   </si>
@@ -162,6 +162,30 @@
   </si>
   <si>
     <t>Sale Invalid Exp Date</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>5127240300002051</t>
+  </si>
+  <si>
+    <t>4137190303592354</t>
+  </si>
+  <si>
+    <t>0330</t>
+  </si>
+  <si>
+    <t>978</t>
+  </si>
+  <si>
+    <t>5126760302215782</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>722</t>
   </si>
 </sst>
 </file>
@@ -946,13 +970,13 @@
         <v>21</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -969,13 +993,13 @@
         <v>23</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -992,13 +1016,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
